--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647237</v>
+        <v>122647243</v>
       </c>
       <c r="B2" t="n">
-        <v>90851</v>
+        <v>90829</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552247</v>
+        <v>552270</v>
       </c>
       <c r="R2" t="n">
-        <v>7247152</v>
+        <v>7247175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647238</v>
+        <v>122647289</v>
       </c>
       <c r="B3" t="n">
-        <v>90851</v>
+        <v>82443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552260</v>
+        <v>552271</v>
       </c>
       <c r="R3" t="n">
-        <v>7247168</v>
+        <v>7247317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647299</v>
+        <v>122647238</v>
       </c>
       <c r="B4" t="n">
-        <v>79772</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552271</v>
+        <v>552260</v>
       </c>
       <c r="R4" t="n">
-        <v>7247320</v>
+        <v>7247168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647264</v>
+        <v>122647272</v>
       </c>
       <c r="B5" t="n">
-        <v>90829</v>
+        <v>79766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552237</v>
+        <v>552240</v>
       </c>
       <c r="R5" t="n">
-        <v>7247224</v>
+        <v>7247221</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647249</v>
+        <v>122647266</v>
       </c>
       <c r="B6" t="n">
-        <v>90851</v>
+        <v>79766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552243</v>
+        <v>552261</v>
       </c>
       <c r="R6" t="n">
-        <v>7247191</v>
+        <v>7247255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647298</v>
+        <v>122647284</v>
       </c>
       <c r="B8" t="n">
         <v>79738</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552268</v>
+        <v>552266</v>
       </c>
       <c r="R8" t="n">
-        <v>7247320</v>
+        <v>7247316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647268</v>
+        <v>122647275</v>
       </c>
       <c r="B9" t="n">
-        <v>79773</v>
+        <v>79738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552261</v>
+        <v>552247</v>
       </c>
       <c r="R9" t="n">
-        <v>7247255</v>
+        <v>7247253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647265</v>
+        <v>122647249</v>
       </c>
       <c r="B10" t="n">
-        <v>79738</v>
+        <v>90851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552261</v>
+        <v>552243</v>
       </c>
       <c r="R10" t="n">
-        <v>7247251</v>
+        <v>7247191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647284</v>
+        <v>122647161</v>
       </c>
       <c r="B11" t="n">
         <v>79738</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552266</v>
+        <v>552228</v>
       </c>
       <c r="R11" t="n">
-        <v>7247316</v>
+        <v>7247131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647239</v>
+        <v>122647283</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552259</v>
+        <v>552256</v>
       </c>
       <c r="R12" t="n">
-        <v>7247181</v>
+        <v>7247259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647160</v>
+        <v>122647241</v>
       </c>
       <c r="B13" t="n">
-        <v>79766</v>
+        <v>82443</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552228</v>
+        <v>552232</v>
       </c>
       <c r="R13" t="n">
-        <v>7247130</v>
+        <v>7247145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647272</v>
+        <v>122647239</v>
       </c>
       <c r="B14" t="n">
-        <v>79766</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552240</v>
+        <v>552259</v>
       </c>
       <c r="R14" t="n">
-        <v>7247221</v>
+        <v>7247181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647250</v>
+        <v>122647265</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>79738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552239</v>
+        <v>552261</v>
       </c>
       <c r="R15" t="n">
-        <v>7247211</v>
+        <v>7247251</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,11 +2129,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647275</v>
+        <v>122647250</v>
       </c>
       <c r="B16" t="n">
-        <v>79738</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552247</v>
+        <v>552239</v>
       </c>
       <c r="R16" t="n">
-        <v>7247253</v>
+        <v>7247211</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,6 +2235,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647266</v>
+        <v>122647298</v>
       </c>
       <c r="B17" t="n">
-        <v>79766</v>
+        <v>79738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552261</v>
+        <v>552268</v>
       </c>
       <c r="R17" t="n">
-        <v>7247255</v>
+        <v>7247320</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647241</v>
+        <v>122647268</v>
       </c>
       <c r="B18" t="n">
-        <v>82443</v>
+        <v>79773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552232</v>
+        <v>552261</v>
       </c>
       <c r="R18" t="n">
-        <v>7247145</v>
+        <v>7247255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647289</v>
+        <v>122647299</v>
       </c>
       <c r="B19" t="n">
-        <v>82443</v>
+        <v>79772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
         <v>552271</v>
       </c>
       <c r="R19" t="n">
-        <v>7247317</v>
+        <v>7247320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647283</v>
+        <v>122647160</v>
       </c>
       <c r="B21" t="n">
-        <v>79738</v>
+        <v>79766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552256</v>
+        <v>552228</v>
       </c>
       <c r="R21" t="n">
-        <v>7247259</v>
+        <v>7247130</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647161</v>
+        <v>122647237</v>
       </c>
       <c r="B22" t="n">
-        <v>79738</v>
+        <v>90851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552228</v>
+        <v>552247</v>
       </c>
       <c r="R22" t="n">
-        <v>7247131</v>
+        <v>7247152</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647243</v>
+        <v>122647264</v>
       </c>
       <c r="B23" t="n">
         <v>90829</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552270</v>
+        <v>552237</v>
       </c>
       <c r="R23" t="n">
-        <v>7247175</v>
+        <v>7247224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647243</v>
+        <v>122647237</v>
       </c>
       <c r="B2" t="n">
-        <v>90829</v>
+        <v>90852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552270</v>
+        <v>552247</v>
       </c>
       <c r="R2" t="n">
-        <v>7247175</v>
+        <v>7247152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647289</v>
+        <v>122647160</v>
       </c>
       <c r="B3" t="n">
-        <v>82443</v>
+        <v>79767</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552271</v>
+        <v>552228</v>
       </c>
       <c r="R3" t="n">
-        <v>7247317</v>
+        <v>7247130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647238</v>
+        <v>122647284</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>79739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552260</v>
+        <v>552266</v>
       </c>
       <c r="R4" t="n">
-        <v>7247168</v>
+        <v>7247316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647272</v>
+        <v>122647241</v>
       </c>
       <c r="B5" t="n">
-        <v>79766</v>
+        <v>82444</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552240</v>
+        <v>552232</v>
       </c>
       <c r="R5" t="n">
-        <v>7247221</v>
+        <v>7247145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647266</v>
+        <v>122647272</v>
       </c>
       <c r="B6" t="n">
-        <v>79766</v>
+        <v>79767</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552261</v>
+        <v>552240</v>
       </c>
       <c r="R6" t="n">
-        <v>7247255</v>
+        <v>7247221</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647159</v>
+        <v>122647266</v>
       </c>
       <c r="B7" t="n">
-        <v>79772</v>
+        <v>79767</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552229</v>
+        <v>552261</v>
       </c>
       <c r="R7" t="n">
-        <v>7247131</v>
+        <v>7247255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647284</v>
+        <v>122647249</v>
       </c>
       <c r="B8" t="n">
-        <v>79738</v>
+        <v>90852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552266</v>
+        <v>552243</v>
       </c>
       <c r="R8" t="n">
-        <v>7247316</v>
+        <v>7247191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647275</v>
+        <v>122647299</v>
       </c>
       <c r="B9" t="n">
-        <v>79738</v>
+        <v>79773</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552247</v>
+        <v>552271</v>
       </c>
       <c r="R9" t="n">
-        <v>7247253</v>
+        <v>7247320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647249</v>
+        <v>122647243</v>
       </c>
       <c r="B10" t="n">
-        <v>90851</v>
+        <v>90830</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552243</v>
+        <v>552270</v>
       </c>
       <c r="R10" t="n">
-        <v>7247191</v>
+        <v>7247175</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647161</v>
+        <v>122647265</v>
       </c>
       <c r="B11" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552228</v>
+        <v>552261</v>
       </c>
       <c r="R11" t="n">
-        <v>7247131</v>
+        <v>7247251</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1738,7 +1738,7 @@
         <v>122647283</v>
       </c>
       <c r="B12" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647241</v>
+        <v>122647238</v>
       </c>
       <c r="B13" t="n">
-        <v>82443</v>
+        <v>90852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552232</v>
+        <v>552260</v>
       </c>
       <c r="R13" t="n">
-        <v>7247145</v>
+        <v>7247168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647239</v>
+        <v>122647289</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>82444</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552259</v>
+        <v>552271</v>
       </c>
       <c r="R14" t="n">
-        <v>7247181</v>
+        <v>7247317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647265</v>
+        <v>122647300</v>
       </c>
       <c r="B15" t="n">
-        <v>79738</v>
+        <v>79767</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552261</v>
+        <v>552271</v>
       </c>
       <c r="R15" t="n">
-        <v>7247251</v>
+        <v>7247319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647250</v>
+        <v>122647275</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>79739</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552239</v>
+        <v>552247</v>
       </c>
       <c r="R16" t="n">
-        <v>7247211</v>
+        <v>7247253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,11 +2235,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647298</v>
+        <v>122647161</v>
       </c>
       <c r="B17" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552268</v>
+        <v>552228</v>
       </c>
       <c r="R17" t="n">
-        <v>7247320</v>
+        <v>7247131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647268</v>
+        <v>122647298</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>79739</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552261</v>
+        <v>552268</v>
       </c>
       <c r="R18" t="n">
-        <v>7247255</v>
+        <v>7247320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2482,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647299</v>
+        <v>122647159</v>
       </c>
       <c r="B19" t="n">
-        <v>79772</v>
+        <v>79773</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552271</v>
+        <v>552229</v>
       </c>
       <c r="R19" t="n">
-        <v>7247320</v>
+        <v>7247131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647300</v>
+        <v>122647250</v>
       </c>
       <c r="B20" t="n">
-        <v>79766</v>
+        <v>57495</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552271</v>
+        <v>552239</v>
       </c>
       <c r="R20" t="n">
-        <v>7247319</v>
+        <v>7247211</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,6 +2661,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647160</v>
+        <v>122647268</v>
       </c>
       <c r="B21" t="n">
-        <v>79766</v>
+        <v>79774</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552228</v>
+        <v>552261</v>
       </c>
       <c r="R21" t="n">
-        <v>7247130</v>
+        <v>7247255</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647237</v>
+        <v>122647264</v>
       </c>
       <c r="B22" t="n">
-        <v>90851</v>
+        <v>90830</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552247</v>
+        <v>552237</v>
       </c>
       <c r="R22" t="n">
-        <v>7247152</v>
+        <v>7247224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647264</v>
+        <v>122647239</v>
       </c>
       <c r="B23" t="n">
-        <v>90829</v>
+        <v>78657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552237</v>
+        <v>552259</v>
       </c>
       <c r="R23" t="n">
-        <v>7247224</v>
+        <v>7247181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647237</v>
+        <v>122647241</v>
       </c>
       <c r="B2" t="n">
-        <v>90852</v>
+        <v>82444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552247</v>
+        <v>552232</v>
       </c>
       <c r="R2" t="n">
-        <v>7247152</v>
+        <v>7247145</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647160</v>
+        <v>122647237</v>
       </c>
       <c r="B3" t="n">
-        <v>79767</v>
+        <v>90852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552228</v>
+        <v>552247</v>
       </c>
       <c r="R3" t="n">
-        <v>7247130</v>
+        <v>7247152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647284</v>
+        <v>122647160</v>
       </c>
       <c r="B4" t="n">
-        <v>79739</v>
+        <v>79767</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552266</v>
+        <v>552228</v>
       </c>
       <c r="R4" t="n">
-        <v>7247316</v>
+        <v>7247130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647241</v>
+        <v>122647284</v>
       </c>
       <c r="B5" t="n">
-        <v>82444</v>
+        <v>79739</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552232</v>
+        <v>552266</v>
       </c>
       <c r="R5" t="n">
-        <v>7247145</v>
+        <v>7247316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647241</v>
+        <v>122647159</v>
       </c>
       <c r="B2" t="n">
-        <v>82444</v>
+        <v>79776</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552232</v>
+        <v>552229</v>
       </c>
       <c r="R2" t="n">
-        <v>7247145</v>
+        <v>7247131</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647237</v>
+        <v>122647283</v>
       </c>
       <c r="B3" t="n">
-        <v>90852</v>
+        <v>79742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552247</v>
+        <v>552256</v>
       </c>
       <c r="R3" t="n">
-        <v>7247152</v>
+        <v>7247259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647160</v>
+        <v>122647249</v>
       </c>
       <c r="B4" t="n">
-        <v>79767</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552228</v>
+        <v>552243</v>
       </c>
       <c r="R4" t="n">
-        <v>7247130</v>
+        <v>7247191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647284</v>
+        <v>122647272</v>
       </c>
       <c r="B5" t="n">
-        <v>79739</v>
+        <v>79770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552266</v>
+        <v>552240</v>
       </c>
       <c r="R5" t="n">
-        <v>7247316</v>
+        <v>7247221</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647272</v>
+        <v>122647265</v>
       </c>
       <c r="B6" t="n">
-        <v>79767</v>
+        <v>79742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552240</v>
+        <v>552261</v>
       </c>
       <c r="R6" t="n">
-        <v>7247221</v>
+        <v>7247251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647266</v>
+        <v>122647298</v>
       </c>
       <c r="B7" t="n">
-        <v>79767</v>
+        <v>79742</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552261</v>
+        <v>552268</v>
       </c>
       <c r="R7" t="n">
-        <v>7247255</v>
+        <v>7247320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647249</v>
+        <v>122647241</v>
       </c>
       <c r="B8" t="n">
-        <v>90852</v>
+        <v>82447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552243</v>
+        <v>552232</v>
       </c>
       <c r="R8" t="n">
-        <v>7247191</v>
+        <v>7247145</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647299</v>
+        <v>122647289</v>
       </c>
       <c r="B9" t="n">
-        <v>79773</v>
+        <v>82447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
         <v>552271</v>
       </c>
       <c r="R9" t="n">
-        <v>7247320</v>
+        <v>7247317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647243</v>
+        <v>122647268</v>
       </c>
       <c r="B10" t="n">
-        <v>90830</v>
+        <v>79777</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552270</v>
+        <v>552261</v>
       </c>
       <c r="R10" t="n">
-        <v>7247175</v>
+        <v>7247255</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647265</v>
+        <v>122647160</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552261</v>
+        <v>552228</v>
       </c>
       <c r="R11" t="n">
-        <v>7247251</v>
+        <v>7247130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647283</v>
+        <v>122647284</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>79742</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552256</v>
+        <v>552266</v>
       </c>
       <c r="R12" t="n">
-        <v>7247259</v>
+        <v>7247316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647238</v>
+        <v>122647264</v>
       </c>
       <c r="B13" t="n">
-        <v>90852</v>
+        <v>90833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552260</v>
+        <v>552237</v>
       </c>
       <c r="R13" t="n">
-        <v>7247168</v>
+        <v>7247224</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647289</v>
+        <v>122647266</v>
       </c>
       <c r="B14" t="n">
-        <v>82444</v>
+        <v>79770</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R14" t="n">
-        <v>7247317</v>
+        <v>7247255</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647300</v>
+        <v>122647237</v>
       </c>
       <c r="B15" t="n">
-        <v>79767</v>
+        <v>90855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552271</v>
+        <v>552247</v>
       </c>
       <c r="R15" t="n">
-        <v>7247319</v>
+        <v>7247152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647275</v>
+        <v>122647239</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552247</v>
+        <v>552259</v>
       </c>
       <c r="R16" t="n">
-        <v>7247253</v>
+        <v>7247181</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2268,7 +2268,7 @@
         <v>122647161</v>
       </c>
       <c r="B17" t="n">
-        <v>79739</v>
+        <v>79742</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647298</v>
+        <v>122647250</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>57495</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552268</v>
+        <v>552239</v>
       </c>
       <c r="R18" t="n">
-        <v>7247320</v>
+        <v>7247211</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,6 +2449,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647159</v>
+        <v>122647275</v>
       </c>
       <c r="B19" t="n">
-        <v>79773</v>
+        <v>79742</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552229</v>
+        <v>552247</v>
       </c>
       <c r="R19" t="n">
-        <v>7247131</v>
+        <v>7247253</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647250</v>
+        <v>122647238</v>
       </c>
       <c r="B20" t="n">
-        <v>57495</v>
+        <v>90855</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552239</v>
+        <v>552260</v>
       </c>
       <c r="R20" t="n">
-        <v>7247211</v>
+        <v>7247168</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,11 +2666,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647268</v>
+        <v>122647243</v>
       </c>
       <c r="B21" t="n">
-        <v>79774</v>
+        <v>90833</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552261</v>
+        <v>552270</v>
       </c>
       <c r="R21" t="n">
-        <v>7247255</v>
+        <v>7247175</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647264</v>
+        <v>122647300</v>
       </c>
       <c r="B22" t="n">
-        <v>90830</v>
+        <v>79770</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552237</v>
+        <v>552271</v>
       </c>
       <c r="R22" t="n">
-        <v>7247224</v>
+        <v>7247319</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647239</v>
+        <v>122647299</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>79776</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,20 +2918,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552259</v>
+        <v>552271</v>
       </c>
       <c r="R23" t="n">
-        <v>7247181</v>
+        <v>7247320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647159</v>
+        <v>122647160</v>
       </c>
       <c r="B2" t="n">
-        <v>79776</v>
+        <v>79770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552229</v>
+        <v>552228</v>
       </c>
       <c r="R2" t="n">
-        <v>7247131</v>
+        <v>7247130</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647283</v>
+        <v>122647250</v>
       </c>
       <c r="B3" t="n">
-        <v>79742</v>
+        <v>57495</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552256</v>
+        <v>552239</v>
       </c>
       <c r="R3" t="n">
-        <v>7247259</v>
+        <v>7247211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,6 +859,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -876,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647249</v>
+        <v>122647289</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
+        <v>82447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552243</v>
+        <v>552271</v>
       </c>
       <c r="R4" t="n">
-        <v>7247191</v>
+        <v>7247317</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647272</v>
+        <v>122647298</v>
       </c>
       <c r="B5" t="n">
-        <v>79770</v>
+        <v>79742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552240</v>
+        <v>552268</v>
       </c>
       <c r="R5" t="n">
-        <v>7247221</v>
+        <v>7247320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647265</v>
+        <v>122647161</v>
       </c>
       <c r="B6" t="n">
         <v>79742</v>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552261</v>
+        <v>552228</v>
       </c>
       <c r="R6" t="n">
-        <v>7247251</v>
+        <v>7247131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647298</v>
+        <v>122647265</v>
       </c>
       <c r="B7" t="n">
         <v>79742</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552268</v>
+        <v>552261</v>
       </c>
       <c r="R7" t="n">
-        <v>7247320</v>
+        <v>7247251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647241</v>
+        <v>122647275</v>
       </c>
       <c r="B8" t="n">
-        <v>82447</v>
+        <v>79742</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552232</v>
+        <v>552247</v>
       </c>
       <c r="R8" t="n">
-        <v>7247145</v>
+        <v>7247253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647289</v>
+        <v>122647266</v>
       </c>
       <c r="B9" t="n">
-        <v>82447</v>
+        <v>79770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R9" t="n">
-        <v>7247317</v>
+        <v>7247255</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647268</v>
+        <v>122647239</v>
       </c>
       <c r="B10" t="n">
-        <v>79777</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552261</v>
+        <v>552259</v>
       </c>
       <c r="R10" t="n">
-        <v>7247255</v>
+        <v>7247181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647160</v>
+        <v>122647159</v>
       </c>
       <c r="B11" t="n">
-        <v>79770</v>
+        <v>79776</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552228</v>
+        <v>552229</v>
       </c>
       <c r="R11" t="n">
-        <v>7247130</v>
+        <v>7247131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647284</v>
+        <v>122647300</v>
       </c>
       <c r="B12" t="n">
-        <v>79742</v>
+        <v>79770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552266</v>
+        <v>552271</v>
       </c>
       <c r="R12" t="n">
-        <v>7247316</v>
+        <v>7247319</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647264</v>
+        <v>122647237</v>
       </c>
       <c r="B13" t="n">
-        <v>90833</v>
+        <v>90855</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552237</v>
+        <v>552247</v>
       </c>
       <c r="R13" t="n">
-        <v>7247224</v>
+        <v>7247152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647266</v>
+        <v>122647241</v>
       </c>
       <c r="B14" t="n">
-        <v>79770</v>
+        <v>82447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552261</v>
+        <v>552232</v>
       </c>
       <c r="R14" t="n">
-        <v>7247255</v>
+        <v>7247145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647237</v>
+        <v>122647284</v>
       </c>
       <c r="B15" t="n">
-        <v>90855</v>
+        <v>79742</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552247</v>
+        <v>552266</v>
       </c>
       <c r="R15" t="n">
-        <v>7247152</v>
+        <v>7247316</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647239</v>
+        <v>122647243</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>90833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552259</v>
+        <v>552270</v>
       </c>
       <c r="R16" t="n">
-        <v>7247181</v>
+        <v>7247175</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647161</v>
+        <v>122647283</v>
       </c>
       <c r="B17" t="n">
         <v>79742</v>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552228</v>
+        <v>552256</v>
       </c>
       <c r="R17" t="n">
-        <v>7247131</v>
+        <v>7247259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647250</v>
+        <v>122647268</v>
       </c>
       <c r="B18" t="n">
-        <v>57495</v>
+        <v>79777</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552239</v>
+        <v>552261</v>
       </c>
       <c r="R18" t="n">
-        <v>7247211</v>
+        <v>7247255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,11 +2452,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647275</v>
+        <v>122647264</v>
       </c>
       <c r="B19" t="n">
-        <v>79742</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552247</v>
+        <v>552237</v>
       </c>
       <c r="R19" t="n">
-        <v>7247253</v>
+        <v>7247224</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647238</v>
+        <v>122647299</v>
       </c>
       <c r="B20" t="n">
-        <v>90855</v>
+        <v>79776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552260</v>
+        <v>552271</v>
       </c>
       <c r="R20" t="n">
-        <v>7247168</v>
+        <v>7247320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647243</v>
+        <v>122647272</v>
       </c>
       <c r="B21" t="n">
-        <v>90833</v>
+        <v>79770</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552270</v>
+        <v>552240</v>
       </c>
       <c r="R21" t="n">
-        <v>7247175</v>
+        <v>7247221</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647300</v>
+        <v>122647238</v>
       </c>
       <c r="B22" t="n">
-        <v>79770</v>
+        <v>90855</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552271</v>
+        <v>552260</v>
       </c>
       <c r="R22" t="n">
-        <v>7247319</v>
+        <v>7247168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647299</v>
+        <v>122647249</v>
       </c>
       <c r="B23" t="n">
-        <v>79776</v>
+        <v>90855</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552271</v>
+        <v>552243</v>
       </c>
       <c r="R23" t="n">
-        <v>7247320</v>
+        <v>7247191</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647250</v>
+        <v>122647289</v>
       </c>
       <c r="B3" t="n">
-        <v>57495</v>
+        <v>82447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552239</v>
+        <v>552271</v>
       </c>
       <c r="R3" t="n">
-        <v>7247211</v>
+        <v>7247317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647289</v>
+        <v>122647250</v>
       </c>
       <c r="B4" t="n">
-        <v>82447</v>
+        <v>57495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552271</v>
+        <v>552239</v>
       </c>
       <c r="R4" t="n">
-        <v>7247317</v>
+        <v>7247211</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647275</v>
+        <v>122647266</v>
       </c>
       <c r="B8" t="n">
-        <v>79742</v>
+        <v>79770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552247</v>
+        <v>552261</v>
       </c>
       <c r="R8" t="n">
-        <v>7247253</v>
+        <v>7247255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647266</v>
+        <v>122647239</v>
       </c>
       <c r="B9" t="n">
-        <v>79770</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552261</v>
+        <v>552259</v>
       </c>
       <c r="R9" t="n">
-        <v>7247255</v>
+        <v>7247181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647239</v>
+        <v>122647275</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>79742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552259</v>
+        <v>552247</v>
       </c>
       <c r="R10" t="n">
-        <v>7247181</v>
+        <v>7247253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647241</v>
+        <v>122647268</v>
       </c>
       <c r="B14" t="n">
-        <v>82447</v>
+        <v>79777</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552232</v>
+        <v>552261</v>
       </c>
       <c r="R14" t="n">
-        <v>7247145</v>
+        <v>7247255</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647284</v>
+        <v>122647241</v>
       </c>
       <c r="B15" t="n">
-        <v>79742</v>
+        <v>82447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552266</v>
+        <v>552232</v>
       </c>
       <c r="R15" t="n">
-        <v>7247316</v>
+        <v>7247145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647243</v>
+        <v>122647284</v>
       </c>
       <c r="B16" t="n">
-        <v>90833</v>
+        <v>79742</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552270</v>
+        <v>552266</v>
       </c>
       <c r="R16" t="n">
-        <v>7247175</v>
+        <v>7247316</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647283</v>
+        <v>122647243</v>
       </c>
       <c r="B17" t="n">
-        <v>79742</v>
+        <v>90833</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552256</v>
+        <v>552270</v>
       </c>
       <c r="R17" t="n">
-        <v>7247259</v>
+        <v>7247175</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647268</v>
+        <v>122647283</v>
       </c>
       <c r="B18" t="n">
-        <v>79777</v>
+        <v>79742</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552261</v>
+        <v>552256</v>
       </c>
       <c r="R18" t="n">
-        <v>7247255</v>
+        <v>7247259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647266</v>
+        <v>122647275</v>
       </c>
       <c r="B8" t="n">
-        <v>79770</v>
+        <v>79742</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552261</v>
+        <v>552247</v>
       </c>
       <c r="R8" t="n">
-        <v>7247255</v>
+        <v>7247253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647239</v>
+        <v>122647266</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
+        <v>79770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552259</v>
+        <v>552261</v>
       </c>
       <c r="R9" t="n">
-        <v>7247181</v>
+        <v>7247255</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647275</v>
+        <v>122647239</v>
       </c>
       <c r="B10" t="n">
-        <v>79742</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552247</v>
+        <v>552259</v>
       </c>
       <c r="R10" t="n">
-        <v>7247253</v>
+        <v>7247181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647275</v>
+        <v>122647266</v>
       </c>
       <c r="B8" t="n">
-        <v>79742</v>
+        <v>79770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552247</v>
+        <v>552261</v>
       </c>
       <c r="R8" t="n">
-        <v>7247253</v>
+        <v>7247255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647266</v>
+        <v>122647239</v>
       </c>
       <c r="B9" t="n">
-        <v>79770</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552261</v>
+        <v>552259</v>
       </c>
       <c r="R9" t="n">
-        <v>7247255</v>
+        <v>7247181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647239</v>
+        <v>122647275</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>79742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552259</v>
+        <v>552247</v>
       </c>
       <c r="R10" t="n">
-        <v>7247181</v>
+        <v>7247253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647268</v>
+        <v>122647241</v>
       </c>
       <c r="B14" t="n">
-        <v>79777</v>
+        <v>82447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552261</v>
+        <v>552232</v>
       </c>
       <c r="R14" t="n">
-        <v>7247255</v>
+        <v>7247145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647241</v>
+        <v>122647284</v>
       </c>
       <c r="B15" t="n">
-        <v>82447</v>
+        <v>79742</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552232</v>
+        <v>552266</v>
       </c>
       <c r="R15" t="n">
-        <v>7247145</v>
+        <v>7247316</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647284</v>
+        <v>122647243</v>
       </c>
       <c r="B16" t="n">
-        <v>79742</v>
+        <v>90833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552266</v>
+        <v>552270</v>
       </c>
       <c r="R16" t="n">
-        <v>7247316</v>
+        <v>7247175</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647243</v>
+        <v>122647283</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>79742</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552270</v>
+        <v>552256</v>
       </c>
       <c r="R17" t="n">
-        <v>7247175</v>
+        <v>7247259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647283</v>
+        <v>122647268</v>
       </c>
       <c r="B18" t="n">
-        <v>79742</v>
+        <v>79777</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552256</v>
+        <v>552261</v>
       </c>
       <c r="R18" t="n">
-        <v>7247259</v>
+        <v>7247255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647241</v>
+        <v>122647268</v>
       </c>
       <c r="B14" t="n">
-        <v>82447</v>
+        <v>79777</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552232</v>
+        <v>552261</v>
       </c>
       <c r="R14" t="n">
-        <v>7247145</v>
+        <v>7247255</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647284</v>
+        <v>122647241</v>
       </c>
       <c r="B15" t="n">
-        <v>79742</v>
+        <v>82447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552266</v>
+        <v>552232</v>
       </c>
       <c r="R15" t="n">
-        <v>7247316</v>
+        <v>7247145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647243</v>
+        <v>122647284</v>
       </c>
       <c r="B16" t="n">
-        <v>90833</v>
+        <v>79742</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552270</v>
+        <v>552266</v>
       </c>
       <c r="R16" t="n">
-        <v>7247175</v>
+        <v>7247316</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647283</v>
+        <v>122647243</v>
       </c>
       <c r="B17" t="n">
-        <v>79742</v>
+        <v>90833</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552256</v>
+        <v>552270</v>
       </c>
       <c r="R17" t="n">
-        <v>7247259</v>
+        <v>7247175</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647268</v>
+        <v>122647283</v>
       </c>
       <c r="B18" t="n">
-        <v>79777</v>
+        <v>79742</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552261</v>
+        <v>552256</v>
       </c>
       <c r="R18" t="n">
-        <v>7247255</v>
+        <v>7247259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647160</v>
+        <v>122647264</v>
       </c>
       <c r="B2" t="n">
-        <v>79770</v>
+        <v>90936</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552228</v>
+        <v>552237</v>
       </c>
       <c r="R2" t="n">
-        <v>7247130</v>
+        <v>7247224</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647289</v>
+        <v>122647250</v>
       </c>
       <c r="B3" t="n">
-        <v>82447</v>
+        <v>57589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552271</v>
+        <v>552239</v>
       </c>
       <c r="R3" t="n">
-        <v>7247317</v>
+        <v>7247211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647250</v>
+        <v>122647299</v>
       </c>
       <c r="B4" t="n">
-        <v>57495</v>
+        <v>79878</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552239</v>
+        <v>552271</v>
       </c>
       <c r="R4" t="n">
-        <v>7247211</v>
+        <v>7247320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +970,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647298</v>
+        <v>122647241</v>
       </c>
       <c r="B5" t="n">
-        <v>79742</v>
+        <v>82549</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552268</v>
+        <v>552232</v>
       </c>
       <c r="R5" t="n">
-        <v>7247320</v>
+        <v>7247145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647161</v>
+        <v>122647284</v>
       </c>
       <c r="B6" t="n">
-        <v>79742</v>
+        <v>79844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552228</v>
+        <v>552266</v>
       </c>
       <c r="R6" t="n">
-        <v>7247131</v>
+        <v>7247316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647265</v>
+        <v>122647159</v>
       </c>
       <c r="B7" t="n">
-        <v>79742</v>
+        <v>79878</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552261</v>
+        <v>552229</v>
       </c>
       <c r="R7" t="n">
-        <v>7247251</v>
+        <v>7247131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647275</v>
+        <v>122647272</v>
       </c>
       <c r="B8" t="n">
-        <v>79742</v>
+        <v>79872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552247</v>
+        <v>552240</v>
       </c>
       <c r="R8" t="n">
-        <v>7247253</v>
+        <v>7247221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647266</v>
+        <v>122647239</v>
       </c>
       <c r="B9" t="n">
-        <v>79770</v>
+        <v>78762</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552261</v>
+        <v>552259</v>
       </c>
       <c r="R9" t="n">
-        <v>7247255</v>
+        <v>7247181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647239</v>
+        <v>122647161</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>79844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552259</v>
+        <v>552228</v>
       </c>
       <c r="R10" t="n">
-        <v>7247181</v>
+        <v>7247131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647159</v>
+        <v>122647298</v>
       </c>
       <c r="B11" t="n">
-        <v>79776</v>
+        <v>79844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552229</v>
+        <v>552268</v>
       </c>
       <c r="R11" t="n">
-        <v>7247131</v>
+        <v>7247320</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647300</v>
+        <v>122647265</v>
       </c>
       <c r="B12" t="n">
-        <v>79770</v>
+        <v>79844</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R12" t="n">
-        <v>7247319</v>
+        <v>7247251</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647237</v>
+        <v>122647289</v>
       </c>
       <c r="B13" t="n">
-        <v>90855</v>
+        <v>82549</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552247</v>
+        <v>552271</v>
       </c>
       <c r="R13" t="n">
-        <v>7247152</v>
+        <v>7247317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647268</v>
+        <v>122647300</v>
       </c>
       <c r="B14" t="n">
-        <v>79777</v>
+        <v>79872</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552261</v>
+        <v>552271</v>
       </c>
       <c r="R14" t="n">
-        <v>7247255</v>
+        <v>7247319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647241</v>
+        <v>122647243</v>
       </c>
       <c r="B15" t="n">
-        <v>82447</v>
+        <v>90936</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552232</v>
+        <v>552270</v>
       </c>
       <c r="R15" t="n">
-        <v>7247145</v>
+        <v>7247175</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647284</v>
+        <v>122647283</v>
       </c>
       <c r="B16" t="n">
-        <v>79742</v>
+        <v>79844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552266</v>
+        <v>552256</v>
       </c>
       <c r="R16" t="n">
-        <v>7247316</v>
+        <v>7247259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647243</v>
+        <v>122647237</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>90958</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552270</v>
+        <v>552247</v>
       </c>
       <c r="R17" t="n">
-        <v>7247175</v>
+        <v>7247152</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647283</v>
+        <v>122647275</v>
       </c>
       <c r="B18" t="n">
-        <v>79742</v>
+        <v>79844</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552256</v>
+        <v>552247</v>
       </c>
       <c r="R18" t="n">
-        <v>7247259</v>
+        <v>7247253</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647264</v>
+        <v>122647238</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>90958</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552237</v>
+        <v>552260</v>
       </c>
       <c r="R19" t="n">
-        <v>7247224</v>
+        <v>7247168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647299</v>
+        <v>122647268</v>
       </c>
       <c r="B20" t="n">
-        <v>79776</v>
+        <v>79879</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R20" t="n">
-        <v>7247320</v>
+        <v>7247255</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647272</v>
+        <v>122647266</v>
       </c>
       <c r="B21" t="n">
-        <v>79770</v>
+        <v>79872</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552240</v>
+        <v>552261</v>
       </c>
       <c r="R21" t="n">
-        <v>7247221</v>
+        <v>7247255</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647238</v>
+        <v>122647249</v>
       </c>
       <c r="B22" t="n">
-        <v>90855</v>
+        <v>90958</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552260</v>
+        <v>552243</v>
       </c>
       <c r="R22" t="n">
-        <v>7247168</v>
+        <v>7247191</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647249</v>
+        <v>122647160</v>
       </c>
       <c r="B23" t="n">
-        <v>90855</v>
+        <v>79872</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552243</v>
+        <v>552228</v>
       </c>
       <c r="R23" t="n">
-        <v>7247191</v>
+        <v>7247130</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647239</v>
+        <v>122647161</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>79844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552259</v>
+        <v>552228</v>
       </c>
       <c r="R9" t="n">
-        <v>7247181</v>
+        <v>7247131</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647161</v>
+        <v>122647239</v>
       </c>
       <c r="B10" t="n">
-        <v>79844</v>
+        <v>78762</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552228</v>
+        <v>552259</v>
       </c>
       <c r="R10" t="n">
-        <v>7247131</v>
+        <v>7247181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647264</v>
+        <v>122647161</v>
       </c>
       <c r="B2" t="n">
-        <v>90936</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552237</v>
+        <v>552228</v>
       </c>
       <c r="R2" t="n">
-        <v>7247224</v>
+        <v>7247131</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647250</v>
+        <v>122647265</v>
       </c>
       <c r="B3" t="n">
-        <v>57589</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552239</v>
+        <v>552261</v>
       </c>
       <c r="R3" t="n">
-        <v>7247211</v>
+        <v>7247251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647299</v>
+        <v>122647298</v>
       </c>
       <c r="B4" t="n">
-        <v>79878</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,7 +927,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552271</v>
+        <v>552268</v>
       </c>
       <c r="R4" t="n">
         <v>7247320</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647241</v>
+        <v>122647250</v>
       </c>
       <c r="B5" t="n">
-        <v>82549</v>
+        <v>57589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552232</v>
+        <v>552239</v>
       </c>
       <c r="R5" t="n">
-        <v>7247145</v>
+        <v>7247211</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647284</v>
+        <v>122647283</v>
       </c>
       <c r="B6" t="n">
-        <v>79844</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552266</v>
+        <v>552256</v>
       </c>
       <c r="R6" t="n">
-        <v>7247316</v>
+        <v>7247259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647159</v>
+        <v>122647237</v>
       </c>
       <c r="B7" t="n">
-        <v>79878</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552229</v>
+        <v>552247</v>
       </c>
       <c r="R7" t="n">
-        <v>7247131</v>
+        <v>7247152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647272</v>
+        <v>122647289</v>
       </c>
       <c r="B8" t="n">
-        <v>79872</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552240</v>
+        <v>552271</v>
       </c>
       <c r="R8" t="n">
-        <v>7247221</v>
+        <v>7247317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647161</v>
+        <v>122647243</v>
       </c>
       <c r="B9" t="n">
-        <v>79844</v>
+        <v>90940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552228</v>
+        <v>552270</v>
       </c>
       <c r="R9" t="n">
-        <v>7247131</v>
+        <v>7247175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647239</v>
+        <v>122647160</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>79876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552259</v>
+        <v>552228</v>
       </c>
       <c r="R10" t="n">
-        <v>7247181</v>
+        <v>7247130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647298</v>
+        <v>122647275</v>
       </c>
       <c r="B11" t="n">
-        <v>79844</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552268</v>
+        <v>552247</v>
       </c>
       <c r="R11" t="n">
-        <v>7247320</v>
+        <v>7247253</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647265</v>
+        <v>122647299</v>
       </c>
       <c r="B12" t="n">
-        <v>79844</v>
+        <v>79882</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552261</v>
+        <v>552271</v>
       </c>
       <c r="R12" t="n">
-        <v>7247251</v>
+        <v>7247320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647289</v>
+        <v>122647264</v>
       </c>
       <c r="B13" t="n">
-        <v>82549</v>
+        <v>90940</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552271</v>
+        <v>552237</v>
       </c>
       <c r="R13" t="n">
-        <v>7247317</v>
+        <v>7247224</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647300</v>
+        <v>122647249</v>
       </c>
       <c r="B14" t="n">
-        <v>79872</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552271</v>
+        <v>552243</v>
       </c>
       <c r="R14" t="n">
-        <v>7247319</v>
+        <v>7247191</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647243</v>
+        <v>122647241</v>
       </c>
       <c r="B15" t="n">
-        <v>90936</v>
+        <v>82553</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552270</v>
+        <v>552232</v>
       </c>
       <c r="R15" t="n">
-        <v>7247175</v>
+        <v>7247145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647283</v>
+        <v>122647284</v>
       </c>
       <c r="B16" t="n">
-        <v>79844</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552256</v>
+        <v>552266</v>
       </c>
       <c r="R16" t="n">
-        <v>7247259</v>
+        <v>7247316</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647237</v>
+        <v>122647268</v>
       </c>
       <c r="B17" t="n">
-        <v>90958</v>
+        <v>79883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552247</v>
+        <v>552261</v>
       </c>
       <c r="R17" t="n">
-        <v>7247152</v>
+        <v>7247255</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647275</v>
+        <v>122647272</v>
       </c>
       <c r="B18" t="n">
-        <v>79844</v>
+        <v>79876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552247</v>
+        <v>552240</v>
       </c>
       <c r="R18" t="n">
-        <v>7247253</v>
+        <v>7247221</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647238</v>
+        <v>122647239</v>
       </c>
       <c r="B19" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552260</v>
+        <v>552259</v>
       </c>
       <c r="R19" t="n">
-        <v>7247168</v>
+        <v>7247181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647268</v>
+        <v>122647159</v>
       </c>
       <c r="B20" t="n">
-        <v>79879</v>
+        <v>79882</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552261</v>
+        <v>552229</v>
       </c>
       <c r="R20" t="n">
-        <v>7247255</v>
+        <v>7247131</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647266</v>
+        <v>122647238</v>
       </c>
       <c r="B21" t="n">
-        <v>79872</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552261</v>
+        <v>552260</v>
       </c>
       <c r="R21" t="n">
-        <v>7247255</v>
+        <v>7247168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647249</v>
+        <v>122647300</v>
       </c>
       <c r="B22" t="n">
-        <v>90958</v>
+        <v>79876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552243</v>
+        <v>552271</v>
       </c>
       <c r="R22" t="n">
-        <v>7247191</v>
+        <v>7247319</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647160</v>
+        <v>122647266</v>
       </c>
       <c r="B23" t="n">
-        <v>79872</v>
+        <v>79876</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552228</v>
+        <v>552261</v>
       </c>
       <c r="R23" t="n">
-        <v>7247130</v>
+        <v>7247255</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647249</v>
+        <v>122647241</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552243</v>
+        <v>552232</v>
       </c>
       <c r="R14" t="n">
-        <v>7247191</v>
+        <v>7247145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647241</v>
+        <v>122647249</v>
       </c>
       <c r="B15" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552232</v>
+        <v>552243</v>
       </c>
       <c r="R15" t="n">
-        <v>7247145</v>
+        <v>7247191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647161</v>
+        <v>122647249</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552228</v>
+        <v>552243</v>
       </c>
       <c r="R2" t="n">
-        <v>7247131</v>
+        <v>7247191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647265</v>
+        <v>122647241</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552261</v>
+        <v>552232</v>
       </c>
       <c r="R3" t="n">
-        <v>7247251</v>
+        <v>7247145</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647298</v>
+        <v>122647289</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552268</v>
+        <v>552271</v>
       </c>
       <c r="R4" t="n">
-        <v>7247320</v>
+        <v>7247317</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647250</v>
+        <v>122647161</v>
       </c>
       <c r="B5" t="n">
-        <v>57589</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552239</v>
+        <v>552228</v>
       </c>
       <c r="R5" t="n">
-        <v>7247211</v>
+        <v>7247131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1071,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1093,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647283</v>
+        <v>122647264</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>90940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552256</v>
+        <v>552237</v>
       </c>
       <c r="R6" t="n">
-        <v>7247259</v>
+        <v>7247224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647237</v>
+        <v>122647160</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552247</v>
+        <v>552228</v>
       </c>
       <c r="R7" t="n">
-        <v>7247152</v>
+        <v>7247130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647289</v>
+        <v>122647299</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>79882</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,7 +1354,7 @@
         <v>552271</v>
       </c>
       <c r="R8" t="n">
-        <v>7247317</v>
+        <v>7247320</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647243</v>
+        <v>122647275</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552270</v>
+        <v>552247</v>
       </c>
       <c r="R9" t="n">
-        <v>7247175</v>
+        <v>7247253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647160</v>
+        <v>122647300</v>
       </c>
       <c r="B10" t="n">
         <v>79876</v>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552228</v>
+        <v>552271</v>
       </c>
       <c r="R10" t="n">
-        <v>7247130</v>
+        <v>7247319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647275</v>
+        <v>122647243</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552247</v>
+        <v>552270</v>
       </c>
       <c r="R11" t="n">
-        <v>7247253</v>
+        <v>7247175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647299</v>
+        <v>122647265</v>
       </c>
       <c r="B12" t="n">
-        <v>79882</v>
+        <v>79848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R12" t="n">
-        <v>7247320</v>
+        <v>7247251</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647264</v>
+        <v>122647159</v>
       </c>
       <c r="B13" t="n">
-        <v>90940</v>
+        <v>79882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552237</v>
+        <v>552229</v>
       </c>
       <c r="R13" t="n">
-        <v>7247224</v>
+        <v>7247131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647241</v>
+        <v>122647238</v>
       </c>
       <c r="B14" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552232</v>
+        <v>552260</v>
       </c>
       <c r="R14" t="n">
-        <v>7247145</v>
+        <v>7247168</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647249</v>
+        <v>122647237</v>
       </c>
       <c r="B15" t="n">
         <v>90962</v>
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552243</v>
+        <v>552247</v>
       </c>
       <c r="R15" t="n">
-        <v>7247191</v>
+        <v>7247152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647284</v>
+        <v>122647268</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>79883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552266</v>
+        <v>552261</v>
       </c>
       <c r="R16" t="n">
-        <v>7247316</v>
+        <v>7247255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647268</v>
+        <v>122647298</v>
       </c>
       <c r="B17" t="n">
-        <v>79883</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552261</v>
+        <v>552268</v>
       </c>
       <c r="R17" t="n">
-        <v>7247255</v>
+        <v>7247320</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647272</v>
+        <v>122647239</v>
       </c>
       <c r="B18" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552240</v>
+        <v>552259</v>
       </c>
       <c r="R18" t="n">
-        <v>7247221</v>
+        <v>7247181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2482,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647239</v>
+        <v>122647272</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552259</v>
+        <v>552240</v>
       </c>
       <c r="R19" t="n">
-        <v>7247181</v>
+        <v>7247221</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647159</v>
+        <v>122647283</v>
       </c>
       <c r="B20" t="n">
-        <v>79882</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552229</v>
+        <v>552256</v>
       </c>
       <c r="R20" t="n">
-        <v>7247131</v>
+        <v>7247259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647238</v>
+        <v>122647266</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552260</v>
+        <v>552261</v>
       </c>
       <c r="R21" t="n">
-        <v>7247168</v>
+        <v>7247255</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2800,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647300</v>
+        <v>122647250</v>
       </c>
       <c r="B22" t="n">
-        <v>79876</v>
+        <v>57589</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552271</v>
+        <v>552239</v>
       </c>
       <c r="R22" t="n">
-        <v>7247319</v>
+        <v>7247211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,6 +2873,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647266</v>
+        <v>122647284</v>
       </c>
       <c r="B23" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552261</v>
+        <v>552266</v>
       </c>
       <c r="R23" t="n">
-        <v>7247255</v>
+        <v>7247316</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647249</v>
+        <v>122647284</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552243</v>
+        <v>552266</v>
       </c>
       <c r="R2" t="n">
-        <v>7247191</v>
+        <v>7247316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647241</v>
+        <v>122647300</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552232</v>
+        <v>552271</v>
       </c>
       <c r="R3" t="n">
-        <v>7247145</v>
+        <v>7247319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647289</v>
+        <v>122647249</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552271</v>
+        <v>552243</v>
       </c>
       <c r="R4" t="n">
-        <v>7247317</v>
+        <v>7247191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647161</v>
+        <v>122647250</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>57589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552228</v>
+        <v>552239</v>
       </c>
       <c r="R5" t="n">
-        <v>7247131</v>
+        <v>7247211</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1071,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647264</v>
+        <v>122647268</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>79883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552237</v>
+        <v>552261</v>
       </c>
       <c r="R6" t="n">
-        <v>7247224</v>
+        <v>7247255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647160</v>
+        <v>122647265</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552228</v>
+        <v>552261</v>
       </c>
       <c r="R7" t="n">
-        <v>7247130</v>
+        <v>7247251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647299</v>
+        <v>122647160</v>
       </c>
       <c r="B8" t="n">
-        <v>79882</v>
+        <v>79876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552271</v>
+        <v>552228</v>
       </c>
       <c r="R8" t="n">
-        <v>7247320</v>
+        <v>7247130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647275</v>
+        <v>122647161</v>
       </c>
       <c r="B9" t="n">
         <v>79848</v>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552247</v>
+        <v>552228</v>
       </c>
       <c r="R9" t="n">
-        <v>7247253</v>
+        <v>7247131</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647300</v>
+        <v>122647243</v>
       </c>
       <c r="B10" t="n">
-        <v>79876</v>
+        <v>90940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552271</v>
+        <v>552270</v>
       </c>
       <c r="R10" t="n">
-        <v>7247319</v>
+        <v>7247175</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647243</v>
+        <v>122647299</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>79882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552270</v>
+        <v>552271</v>
       </c>
       <c r="R11" t="n">
-        <v>7247175</v>
+        <v>7247320</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1729,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647265</v>
+        <v>122647298</v>
       </c>
       <c r="B12" t="n">
         <v>79848</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552261</v>
+        <v>552268</v>
       </c>
       <c r="R12" t="n">
-        <v>7247251</v>
+        <v>7247320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647159</v>
+        <v>122647239</v>
       </c>
       <c r="B13" t="n">
-        <v>79882</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,20 +1858,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552229</v>
+        <v>552259</v>
       </c>
       <c r="R13" t="n">
-        <v>7247131</v>
+        <v>7247181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647238</v>
+        <v>122647272</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552260</v>
+        <v>552240</v>
       </c>
       <c r="R14" t="n">
-        <v>7247168</v>
+        <v>7247221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2047,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647237</v>
+        <v>122647289</v>
       </c>
       <c r="B15" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552247</v>
+        <v>552271</v>
       </c>
       <c r="R15" t="n">
-        <v>7247152</v>
+        <v>7247317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647268</v>
+        <v>122647241</v>
       </c>
       <c r="B16" t="n">
-        <v>79883</v>
+        <v>82553</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552261</v>
+        <v>552232</v>
       </c>
       <c r="R16" t="n">
-        <v>7247255</v>
+        <v>7247145</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647298</v>
+        <v>122647275</v>
       </c>
       <c r="B17" t="n">
         <v>79848</v>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552268</v>
+        <v>552247</v>
       </c>
       <c r="R17" t="n">
-        <v>7247320</v>
+        <v>7247253</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647239</v>
+        <v>122647159</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,20 +2388,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552259</v>
+        <v>552229</v>
       </c>
       <c r="R18" t="n">
-        <v>7247181</v>
+        <v>7247131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647272</v>
+        <v>122647238</v>
       </c>
       <c r="B19" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552240</v>
+        <v>552260</v>
       </c>
       <c r="R19" t="n">
-        <v>7247221</v>
+        <v>7247168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2795,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647250</v>
+        <v>122647237</v>
       </c>
       <c r="B22" t="n">
-        <v>57589</v>
+        <v>90962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552239</v>
+        <v>552247</v>
       </c>
       <c r="R22" t="n">
-        <v>7247211</v>
+        <v>7247152</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,11 +2878,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647284</v>
+        <v>122647264</v>
       </c>
       <c r="B23" t="n">
-        <v>79848</v>
+        <v>90940</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552266</v>
+        <v>552237</v>
       </c>
       <c r="R23" t="n">
-        <v>7247316</v>
+        <v>7247224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647159</v>
+        <v>122647283</v>
       </c>
       <c r="B18" t="n">
-        <v>79882</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552229</v>
+        <v>552256</v>
       </c>
       <c r="R18" t="n">
-        <v>7247131</v>
+        <v>7247259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647238</v>
+        <v>122647159</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>79882</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552260</v>
+        <v>552229</v>
       </c>
       <c r="R19" t="n">
-        <v>7247168</v>
+        <v>7247131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647283</v>
+        <v>122647238</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552256</v>
+        <v>552260</v>
       </c>
       <c r="R20" t="n">
-        <v>7247259</v>
+        <v>7247168</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647283</v>
+        <v>122647159</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>79882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552256</v>
+        <v>552229</v>
       </c>
       <c r="R18" t="n">
-        <v>7247259</v>
+        <v>7247131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647159</v>
+        <v>122647238</v>
       </c>
       <c r="B19" t="n">
-        <v>79882</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552229</v>
+        <v>552260</v>
       </c>
       <c r="R19" t="n">
-        <v>7247131</v>
+        <v>7247168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647238</v>
+        <v>122647283</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552260</v>
+        <v>552256</v>
       </c>
       <c r="R20" t="n">
-        <v>7247168</v>
+        <v>7247259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647284</v>
+        <v>122647243</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>90940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552266</v>
+        <v>552270</v>
       </c>
       <c r="R2" t="n">
-        <v>7247316</v>
+        <v>7247175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647300</v>
+        <v>122647265</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R3" t="n">
-        <v>7247319</v>
+        <v>7247251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647250</v>
+        <v>122647159</v>
       </c>
       <c r="B5" t="n">
-        <v>57589</v>
+        <v>79882</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552239</v>
+        <v>552229</v>
       </c>
       <c r="R5" t="n">
-        <v>7247211</v>
+        <v>7247131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1071,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1093,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647268</v>
+        <v>122647266</v>
       </c>
       <c r="B6" t="n">
-        <v>79883</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647265</v>
+        <v>122647300</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552261</v>
+        <v>552271</v>
       </c>
       <c r="R7" t="n">
-        <v>7247251</v>
+        <v>7247319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647160</v>
+        <v>122647283</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552228</v>
+        <v>552256</v>
       </c>
       <c r="R8" t="n">
-        <v>7247130</v>
+        <v>7247259</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647161</v>
+        <v>122647298</v>
       </c>
       <c r="B9" t="n">
         <v>79848</v>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552228</v>
+        <v>552268</v>
       </c>
       <c r="R9" t="n">
-        <v>7247131</v>
+        <v>7247320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647243</v>
+        <v>122647272</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>79876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552270</v>
+        <v>552240</v>
       </c>
       <c r="R10" t="n">
-        <v>7247175</v>
+        <v>7247221</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647299</v>
+        <v>122647264</v>
       </c>
       <c r="B11" t="n">
-        <v>79882</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552271</v>
+        <v>552237</v>
       </c>
       <c r="R11" t="n">
-        <v>7247320</v>
+        <v>7247224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647298</v>
+        <v>122647250</v>
       </c>
       <c r="B12" t="n">
-        <v>79848</v>
+        <v>57589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552268</v>
+        <v>552239</v>
       </c>
       <c r="R12" t="n">
-        <v>7247320</v>
+        <v>7247211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,6 +1813,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647239</v>
+        <v>122647237</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552259</v>
+        <v>552247</v>
       </c>
       <c r="R13" t="n">
-        <v>7247181</v>
+        <v>7247152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647272</v>
+        <v>122647275</v>
       </c>
       <c r="B14" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552240</v>
+        <v>552247</v>
       </c>
       <c r="R14" t="n">
-        <v>7247221</v>
+        <v>7247253</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647289</v>
+        <v>122647268</v>
       </c>
       <c r="B15" t="n">
-        <v>82553</v>
+        <v>79883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R15" t="n">
-        <v>7247317</v>
+        <v>7247255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647241</v>
+        <v>122647289</v>
       </c>
       <c r="B16" t="n">
         <v>82553</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552232</v>
+        <v>552271</v>
       </c>
       <c r="R16" t="n">
-        <v>7247145</v>
+        <v>7247317</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647275</v>
+        <v>122647160</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552247</v>
+        <v>552228</v>
       </c>
       <c r="R17" t="n">
-        <v>7247253</v>
+        <v>7247130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,7 +2376,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647159</v>
+        <v>122647299</v>
       </c>
       <c r="B18" t="n">
         <v>79882</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552229</v>
+        <v>552271</v>
       </c>
       <c r="R18" t="n">
-        <v>7247131</v>
+        <v>7247320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647238</v>
+        <v>122647284</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552260</v>
+        <v>552266</v>
       </c>
       <c r="R19" t="n">
-        <v>7247168</v>
+        <v>7247316</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647283</v>
+        <v>122647239</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552256</v>
+        <v>552259</v>
       </c>
       <c r="R20" t="n">
-        <v>7247259</v>
+        <v>7247181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647266</v>
+        <v>122647238</v>
       </c>
       <c r="B21" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552261</v>
+        <v>552260</v>
       </c>
       <c r="R21" t="n">
-        <v>7247255</v>
+        <v>7247168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647237</v>
+        <v>122647161</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552247</v>
+        <v>552228</v>
       </c>
       <c r="R22" t="n">
-        <v>7247152</v>
+        <v>7247131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647264</v>
+        <v>122647241</v>
       </c>
       <c r="B23" t="n">
-        <v>90940</v>
+        <v>82553</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552237</v>
+        <v>552232</v>
       </c>
       <c r="R23" t="n">
-        <v>7247224</v>
+        <v>7247145</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647238</v>
+        <v>122647161</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552260</v>
+        <v>552228</v>
       </c>
       <c r="R21" t="n">
-        <v>7247168</v>
+        <v>7247131</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647161</v>
+        <v>122647238</v>
       </c>
       <c r="B22" t="n">
-        <v>79848</v>
+        <v>90962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552228</v>
+        <v>552260</v>
       </c>
       <c r="R22" t="n">
-        <v>7247131</v>
+        <v>7247168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647161</v>
+        <v>122647238</v>
       </c>
       <c r="B21" t="n">
-        <v>79848</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552228</v>
+        <v>552260</v>
       </c>
       <c r="R21" t="n">
-        <v>7247131</v>
+        <v>7247168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647238</v>
+        <v>122647161</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552260</v>
+        <v>552228</v>
       </c>
       <c r="R22" t="n">
-        <v>7247168</v>
+        <v>7247131</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647243</v>
+        <v>122647298</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552270</v>
+        <v>552268</v>
       </c>
       <c r="R2" t="n">
-        <v>7247175</v>
+        <v>7247320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647265</v>
+        <v>122647237</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552261</v>
+        <v>552247</v>
       </c>
       <c r="R3" t="n">
-        <v>7247251</v>
+        <v>7247152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647249</v>
+        <v>122647243</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552243</v>
+        <v>552270</v>
       </c>
       <c r="R4" t="n">
-        <v>7247191</v>
+        <v>7247175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647159</v>
+        <v>122647160</v>
       </c>
       <c r="B5" t="n">
-        <v>79882</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552229</v>
+        <v>552228</v>
       </c>
       <c r="R5" t="n">
-        <v>7247131</v>
+        <v>7247130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647266</v>
+        <v>122647250</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>57589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552261</v>
+        <v>552239</v>
       </c>
       <c r="R6" t="n">
-        <v>7247255</v>
+        <v>7247211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647300</v>
+        <v>122647241</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552271</v>
+        <v>552232</v>
       </c>
       <c r="R7" t="n">
-        <v>7247319</v>
+        <v>7247145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647283</v>
+        <v>122647300</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552256</v>
+        <v>552271</v>
       </c>
       <c r="R8" t="n">
-        <v>7247259</v>
+        <v>7247319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647298</v>
+        <v>122647238</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552268</v>
+        <v>552260</v>
       </c>
       <c r="R9" t="n">
-        <v>7247320</v>
+        <v>7247168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647272</v>
+        <v>122647264</v>
       </c>
       <c r="B10" t="n">
-        <v>79876</v>
+        <v>90948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552240</v>
+        <v>552237</v>
       </c>
       <c r="R10" t="n">
-        <v>7247221</v>
+        <v>7247224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647264</v>
+        <v>122647161</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552237</v>
+        <v>552228</v>
       </c>
       <c r="R11" t="n">
-        <v>7247224</v>
+        <v>7247131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647250</v>
+        <v>122647283</v>
       </c>
       <c r="B12" t="n">
-        <v>57589</v>
+        <v>79848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552239</v>
+        <v>552256</v>
       </c>
       <c r="R12" t="n">
-        <v>7247211</v>
+        <v>7247259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,11 +1818,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647237</v>
+        <v>122647159</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>79882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552247</v>
+        <v>552229</v>
       </c>
       <c r="R13" t="n">
-        <v>7247152</v>
+        <v>7247131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647275</v>
+        <v>122647268</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>79883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552247</v>
+        <v>552261</v>
       </c>
       <c r="R14" t="n">
-        <v>7247253</v>
+        <v>7247255</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647268</v>
+        <v>122647275</v>
       </c>
       <c r="B15" t="n">
-        <v>79883</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552261</v>
+        <v>552247</v>
       </c>
       <c r="R15" t="n">
-        <v>7247255</v>
+        <v>7247253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647289</v>
+        <v>122647265</v>
       </c>
       <c r="B16" t="n">
-        <v>82553</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R16" t="n">
-        <v>7247317</v>
+        <v>7247251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647160</v>
+        <v>122647249</v>
       </c>
       <c r="B17" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552228</v>
+        <v>552243</v>
       </c>
       <c r="R17" t="n">
-        <v>7247130</v>
+        <v>7247191</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647299</v>
+        <v>122647239</v>
       </c>
       <c r="B18" t="n">
-        <v>79882</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,20 +2388,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552271</v>
+        <v>552259</v>
       </c>
       <c r="R18" t="n">
-        <v>7247320</v>
+        <v>7247181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647239</v>
+        <v>122647266</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552259</v>
+        <v>552261</v>
       </c>
       <c r="R20" t="n">
-        <v>7247181</v>
+        <v>7247255</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647238</v>
+        <v>122647272</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552260</v>
+        <v>552240</v>
       </c>
       <c r="R21" t="n">
-        <v>7247168</v>
+        <v>7247221</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647161</v>
+        <v>122647289</v>
       </c>
       <c r="B22" t="n">
-        <v>79848</v>
+        <v>82553</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552228</v>
+        <v>552271</v>
       </c>
       <c r="R22" t="n">
-        <v>7247131</v>
+        <v>7247317</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647241</v>
+        <v>122647299</v>
       </c>
       <c r="B23" t="n">
-        <v>82553</v>
+        <v>79882</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552232</v>
+        <v>552271</v>
       </c>
       <c r="R23" t="n">
-        <v>7247145</v>
+        <v>7247320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647298</v>
+        <v>122647284</v>
       </c>
       <c r="B2" t="n">
         <v>79848</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552268</v>
+        <v>552266</v>
       </c>
       <c r="R2" t="n">
-        <v>7247320</v>
+        <v>7247316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647237</v>
+        <v>122647241</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552247</v>
+        <v>552232</v>
       </c>
       <c r="R3" t="n">
-        <v>7247152</v>
+        <v>7247145</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647243</v>
+        <v>122647265</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552270</v>
+        <v>552261</v>
       </c>
       <c r="R4" t="n">
-        <v>7247175</v>
+        <v>7247251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647160</v>
+        <v>122647264</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>90948</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552228</v>
+        <v>552237</v>
       </c>
       <c r="R5" t="n">
-        <v>7247130</v>
+        <v>7247224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647250</v>
+        <v>122647237</v>
       </c>
       <c r="B6" t="n">
-        <v>57589</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552239</v>
+        <v>552247</v>
       </c>
       <c r="R6" t="n">
-        <v>7247211</v>
+        <v>7247152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,11 +1177,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647241</v>
+        <v>122647300</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552232</v>
+        <v>552271</v>
       </c>
       <c r="R7" t="n">
-        <v>7247145</v>
+        <v>7247319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647300</v>
+        <v>122647289</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,7 +1354,7 @@
         <v>552271</v>
       </c>
       <c r="R8" t="n">
-        <v>7247319</v>
+        <v>7247317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647238</v>
+        <v>122647283</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552260</v>
+        <v>552256</v>
       </c>
       <c r="R9" t="n">
-        <v>7247168</v>
+        <v>7247259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647264</v>
+        <v>122647159</v>
       </c>
       <c r="B10" t="n">
-        <v>90948</v>
+        <v>79882</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552237</v>
+        <v>552229</v>
       </c>
       <c r="R10" t="n">
-        <v>7247224</v>
+        <v>7247131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647161</v>
+        <v>122647268</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>79883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552228</v>
+        <v>552261</v>
       </c>
       <c r="R11" t="n">
-        <v>7247131</v>
+        <v>7247255</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647283</v>
+        <v>122647266</v>
       </c>
       <c r="B12" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552256</v>
+        <v>552261</v>
       </c>
       <c r="R12" t="n">
-        <v>7247259</v>
+        <v>7247255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647159</v>
+        <v>122647160</v>
       </c>
       <c r="B13" t="n">
-        <v>79882</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552229</v>
+        <v>552228</v>
       </c>
       <c r="R13" t="n">
-        <v>7247131</v>
+        <v>7247130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647268</v>
+        <v>122647299</v>
       </c>
       <c r="B14" t="n">
-        <v>79883</v>
+        <v>79882</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552261</v>
+        <v>552271</v>
       </c>
       <c r="R14" t="n">
-        <v>7247255</v>
+        <v>7247320</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647275</v>
+        <v>122647161</v>
       </c>
       <c r="B15" t="n">
         <v>79848</v>
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552247</v>
+        <v>552228</v>
       </c>
       <c r="R15" t="n">
-        <v>7247253</v>
+        <v>7247131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647265</v>
+        <v>122647238</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552261</v>
+        <v>552260</v>
       </c>
       <c r="R16" t="n">
-        <v>7247251</v>
+        <v>7247168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647249</v>
+        <v>122647250</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
+        <v>57589</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552243</v>
+        <v>552239</v>
       </c>
       <c r="R17" t="n">
-        <v>7247191</v>
+        <v>7247211</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2341,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,7 +2482,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647284</v>
+        <v>122647275</v>
       </c>
       <c r="B19" t="n">
         <v>79848</v>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552266</v>
+        <v>552247</v>
       </c>
       <c r="R19" t="n">
-        <v>7247316</v>
+        <v>7247253</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647266</v>
+        <v>122647243</v>
       </c>
       <c r="B20" t="n">
-        <v>79876</v>
+        <v>90948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552261</v>
+        <v>552270</v>
       </c>
       <c r="R20" t="n">
-        <v>7247255</v>
+        <v>7247175</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647289</v>
+        <v>122647249</v>
       </c>
       <c r="B22" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552271</v>
+        <v>552243</v>
       </c>
       <c r="R22" t="n">
-        <v>7247317</v>
+        <v>7247191</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647299</v>
+        <v>122647298</v>
       </c>
       <c r="B23" t="n">
-        <v>79882</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552271</v>
+        <v>552268</v>
       </c>
       <c r="R23" t="n">
         <v>7247320</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647264</v>
+        <v>122647237</v>
       </c>
       <c r="B5" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552237</v>
+        <v>552247</v>
       </c>
       <c r="R5" t="n">
-        <v>7247224</v>
+        <v>7247152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647237</v>
+        <v>122647264</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552247</v>
+        <v>552237</v>
       </c>
       <c r="R6" t="n">
-        <v>7247152</v>
+        <v>7247224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647161</v>
+        <v>122647238</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552228</v>
+        <v>552260</v>
       </c>
       <c r="R15" t="n">
-        <v>7247131</v>
+        <v>7247168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647238</v>
+        <v>122647161</v>
       </c>
       <c r="B16" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552260</v>
+        <v>552228</v>
       </c>
       <c r="R16" t="n">
-        <v>7247168</v>
+        <v>7247131</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647250</v>
+        <v>122647239</v>
       </c>
       <c r="B17" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552239</v>
+        <v>552259</v>
       </c>
       <c r="R17" t="n">
-        <v>7247211</v>
+        <v>7247181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,11 +2343,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647239</v>
+        <v>122647250</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552259</v>
+        <v>552239</v>
       </c>
       <c r="R18" t="n">
-        <v>7247181</v>
+        <v>7247211</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2449,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647238</v>
+        <v>122647161</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552260</v>
+        <v>552228</v>
       </c>
       <c r="R15" t="n">
-        <v>7247168</v>
+        <v>7247131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647161</v>
+        <v>122647238</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552228</v>
+        <v>552260</v>
       </c>
       <c r="R16" t="n">
-        <v>7247131</v>
+        <v>7247168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647239</v>
+        <v>122647250</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552259</v>
+        <v>552239</v>
       </c>
       <c r="R17" t="n">
-        <v>7247181</v>
+        <v>7247211</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,6 +2343,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647250</v>
+        <v>122647239</v>
       </c>
       <c r="B18" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552239</v>
+        <v>552259</v>
       </c>
       <c r="R18" t="n">
-        <v>7247211</v>
+        <v>7247181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,11 +2454,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647284</v>
+        <v>122647249</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552266</v>
+        <v>552243</v>
       </c>
       <c r="R2" t="n">
-        <v>7247316</v>
+        <v>7247191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647241</v>
+        <v>122647159</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>79882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552232</v>
+        <v>552229</v>
       </c>
       <c r="R3" t="n">
-        <v>7247145</v>
+        <v>7247131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647265</v>
+        <v>122647250</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>57589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552261</v>
+        <v>552239</v>
       </c>
       <c r="R4" t="n">
-        <v>7247251</v>
+        <v>7247211</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647237</v>
+        <v>122647265</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552247</v>
+        <v>552261</v>
       </c>
       <c r="R5" t="n">
-        <v>7247152</v>
+        <v>7247251</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647300</v>
+        <v>122647289</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,7 +1253,7 @@
         <v>552271</v>
       </c>
       <c r="R7" t="n">
-        <v>7247319</v>
+        <v>7247317</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647289</v>
+        <v>122647268</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>79883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R8" t="n">
-        <v>7247317</v>
+        <v>7247255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647283</v>
+        <v>122647298</v>
       </c>
       <c r="B9" t="n">
         <v>79848</v>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552256</v>
+        <v>552268</v>
       </c>
       <c r="R9" t="n">
-        <v>7247259</v>
+        <v>7247320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647159</v>
+        <v>122647241</v>
       </c>
       <c r="B10" t="n">
-        <v>79882</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552229</v>
+        <v>552232</v>
       </c>
       <c r="R10" t="n">
-        <v>7247131</v>
+        <v>7247145</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647268</v>
+        <v>122647161</v>
       </c>
       <c r="B11" t="n">
-        <v>79883</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552261</v>
+        <v>552228</v>
       </c>
       <c r="R11" t="n">
-        <v>7247255</v>
+        <v>7247131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1729,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647266</v>
+        <v>122647299</v>
       </c>
       <c r="B12" t="n">
-        <v>79876</v>
+        <v>79882</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552261</v>
+        <v>552271</v>
       </c>
       <c r="R12" t="n">
-        <v>7247255</v>
+        <v>7247320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647160</v>
+        <v>122647238</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552228</v>
+        <v>552260</v>
       </c>
       <c r="R13" t="n">
-        <v>7247130</v>
+        <v>7247168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647299</v>
+        <v>122647243</v>
       </c>
       <c r="B14" t="n">
-        <v>79882</v>
+        <v>90948</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552271</v>
+        <v>552270</v>
       </c>
       <c r="R14" t="n">
-        <v>7247320</v>
+        <v>7247175</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2047,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647161</v>
+        <v>122647300</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>79876</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552228</v>
+        <v>552271</v>
       </c>
       <c r="R15" t="n">
-        <v>7247131</v>
+        <v>7247319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2164,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647238</v>
+        <v>122647237</v>
       </c>
       <c r="B16" t="n">
         <v>90970</v>
@@ -2199,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552260</v>
+        <v>552247</v>
       </c>
       <c r="R16" t="n">
-        <v>7247168</v>
+        <v>7247152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647250</v>
+        <v>122647275</v>
       </c>
       <c r="B17" t="n">
-        <v>57589</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552239</v>
+        <v>552247</v>
       </c>
       <c r="R17" t="n">
-        <v>7247211</v>
+        <v>7247253</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647239</v>
+        <v>122647284</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552259</v>
+        <v>552266</v>
       </c>
       <c r="R18" t="n">
-        <v>7247181</v>
+        <v>7247316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647275</v>
+        <v>122647239</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552247</v>
+        <v>552259</v>
       </c>
       <c r="R19" t="n">
-        <v>7247253</v>
+        <v>7247181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647243</v>
+        <v>122647160</v>
       </c>
       <c r="B20" t="n">
-        <v>90948</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552270</v>
+        <v>552228</v>
       </c>
       <c r="R20" t="n">
-        <v>7247175</v>
+        <v>7247130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647249</v>
+        <v>122647266</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>79876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552243</v>
+        <v>552261</v>
       </c>
       <c r="R22" t="n">
-        <v>7247191</v>
+        <v>7247255</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647298</v>
+        <v>122647283</v>
       </c>
       <c r="B23" t="n">
         <v>79848</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552268</v>
+        <v>552256</v>
       </c>
       <c r="R23" t="n">
-        <v>7247320</v>
+        <v>7247259</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 24709-2022 artfynd.xlsx
+++ b/artfynd/A 24709-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647249</v>
+        <v>122647243</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552243</v>
+        <v>552270</v>
       </c>
       <c r="R2" t="n">
-        <v>7247191</v>
+        <v>7247175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647159</v>
+        <v>122647264</v>
       </c>
       <c r="B3" t="n">
-        <v>79882</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552229</v>
+        <v>552237</v>
       </c>
       <c r="R3" t="n">
-        <v>7247131</v>
+        <v>7247224</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647250</v>
+        <v>122647241</v>
       </c>
       <c r="B4" t="n">
-        <v>57589</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552239</v>
+        <v>552232</v>
       </c>
       <c r="R4" t="n">
-        <v>7247211</v>
+        <v>7247145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647265</v>
+        <v>122647289</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552261</v>
+        <v>552271</v>
       </c>
       <c r="R5" t="n">
-        <v>7247251</v>
+        <v>7247317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647264</v>
+        <v>122647161</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552237</v>
+        <v>552228</v>
       </c>
       <c r="R6" t="n">
-        <v>7247224</v>
+        <v>7247131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647289</v>
+        <v>122647265</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552271</v>
+        <v>552261</v>
       </c>
       <c r="R7" t="n">
-        <v>7247317</v>
+        <v>7247251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647268</v>
+        <v>122647275</v>
       </c>
       <c r="B8" t="n">
-        <v>79883</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552261</v>
+        <v>552247</v>
       </c>
       <c r="R8" t="n">
-        <v>7247255</v>
+        <v>7247253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647298</v>
+        <v>122647283</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552268</v>
+        <v>552256</v>
       </c>
       <c r="R9" t="n">
-        <v>7247320</v>
+        <v>7247259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647241</v>
+        <v>122647284</v>
       </c>
       <c r="B10" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552232</v>
+        <v>552266</v>
       </c>
       <c r="R10" t="n">
-        <v>7247145</v>
+        <v>7247316</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1634,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647161</v>
+        <v>122647298</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552228</v>
+        <v>552268</v>
       </c>
       <c r="R11" t="n">
-        <v>7247131</v>
+        <v>7247320</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,32 +1685,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647299</v>
+        <v>122647239</v>
       </c>
       <c r="B12" t="n">
-        <v>79882</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1780,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552271</v>
+        <v>552259</v>
       </c>
       <c r="R12" t="n">
-        <v>7247320</v>
+        <v>7247181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647238</v>
+        <v>122647160</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552260</v>
+        <v>552228</v>
       </c>
       <c r="R13" t="n">
-        <v>7247168</v>
+        <v>7247130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647243</v>
+        <v>122647266</v>
       </c>
       <c r="B14" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552270</v>
+        <v>552261</v>
       </c>
       <c r="R14" t="n">
-        <v>7247175</v>
+        <v>7247255</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647300</v>
+        <v>122647272</v>
       </c>
       <c r="B15" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552271</v>
+        <v>552240</v>
       </c>
       <c r="R15" t="n">
-        <v>7247319</v>
+        <v>7247221</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647237</v>
+        <v>122647300</v>
       </c>
       <c r="B16" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552247</v>
+        <v>552271</v>
       </c>
       <c r="R16" t="n">
-        <v>7247152</v>
+        <v>7247319</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647275</v>
+        <v>122647159</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552247</v>
+        <v>552229</v>
       </c>
       <c r="R17" t="n">
-        <v>7247253</v>
+        <v>7247131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,37 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647284</v>
+        <v>122647299</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552266</v>
+        <v>552271</v>
       </c>
       <c r="R18" t="n">
-        <v>7247316</v>
+        <v>7247320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,37 +2392,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647239</v>
+        <v>122647268</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552259</v>
+        <v>552261</v>
       </c>
       <c r="R19" t="n">
-        <v>7247181</v>
+        <v>7247255</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,37 +2493,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647160</v>
+        <v>122647250</v>
       </c>
       <c r="B20" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552228</v>
+        <v>552239</v>
       </c>
       <c r="R20" t="n">
-        <v>7247130</v>
+        <v>7247211</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,6 +2566,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1 födosök</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2683,328 +2588,10 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>122647272</v>
-      </c>
-      <c r="B21" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>552240</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7247221</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>122647266</v>
-      </c>
-      <c r="B22" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>552261</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7247255</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>122647283</v>
-      </c>
-      <c r="B23" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>552256</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7247259</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Hannah Norman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
         <is>
           <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
         </is>
